--- a/app/static/templates/PD.xlsx
+++ b/app/static/templates/PD.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +28,85 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001e293b"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3C5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,12 +114,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001A3C5E"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -410,40 +595,833 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Loan ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SEGMENT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Reporting Month</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Staging</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Loan Amount</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>495000</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0003</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3150000</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0004</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1080000</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0005</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>870000</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0002</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>748000</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0003</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>3100000</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0004</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1060000</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0005</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>860000</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D50000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose from the list: Staging" promptTitle="Staging" prompt="Stage 1 = performing  |  Stage 2 = SICR  |  Stage 3 = default" type="list">
+      <formula1>"Stage 1,Stage 2,Stage 3"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Probability of Default (PD) — Upload Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Upload one or more monthly PD files per run. Each file is a snapshot of your loan book for one or more reporting months. The engine automatically derives month-to-month staging transitions to build an IFRS 9 3×3 transition matrix per segment.  Supply at least 2–3 months of history to obtain meaningful lifetime PD curves.</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="11" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Allowed Values</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Business Rule</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Loan ID</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Any non-empty string</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Must be non-empty. Each (Loan ID, Reporting Month) pair must be unique across all uploaded PD files for this run — duplicates trigger EC-10.</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>SEGMENT</t>
         </is>
       </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Must match a configured segment name</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Case-sensitive match to one of your workspace's Segment names (Workspace → Admin → Segments).</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Reporting Month</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD or Excel date</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>The as-at date for this row. Typically the last calendar day of the reporting month.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Enum</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Stage 1  /  Stage 2  /  Stage 3</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>IFRS 9 credit stage at the reporting date. Case-sensitive. Stage 1 = performing, Stage 2 = significant increase in credit risk (SICR), Stage 3 = credit-impaired / default.</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Loan Amount</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>≥ 0</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Outstanding principal balance at the reporting date. Must be non-negative.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>500000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>How the transition matrix is constructed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>The engine joins each loan's staging in month N with its staging in month N+1.</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • LN-001 is Stage 1 in Jan-25 and Stage 2 in Feb-25  →  Stage 1→Stage 2 transition recorded.</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • LN-001 is Stage 1 in Jan-25 and absent in Feb-25  →  Stage 1→Offbooks (fully repaid/written off).</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>All monthly transitions are summed into a 3×3 aggregate matrix per SEGMENT.</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Row proportions are computed, Stage 1 and Stage 3 rows are normalised (IFRS 9 boundary conditions),</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>and the resulting matrix is raised to powers 1–299 to produce the lifetime PD curve.</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Cure rate = P(Stage 3 → Stage 1) + P(Stage 3 → Stage 2) from the proportion matrix.</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Accepted aliases for Reporting Month column</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>The engine also recognises the column name as:   Reporting Month ("As At")   or   As At</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Multiple files per run (PD only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>PD is the only input type where multiple files can be uploaded per run (up to 10 files, 25 MB each).</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>All files are concatenated and deduplicated on (Loan ID, Reporting Month) before the engine runs.</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>This allows you to split large monthly exports into separate files.</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="11" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>